--- a/正解Input.xlsx
+++ b/正解Input.xlsx
@@ -1,258 +1,64 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="生徒のデータ-2" sheetId="1" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="生徒のデータ-2" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="53">
-  <si>
-    <t>表</t>
-  </si>
-  <si>
-    <t>NO</t>
-  </si>
-  <si>
-    <t>処理対象日付</t>
-  </si>
-  <si>
-    <t>ツール一覧</t>
-  </si>
-  <si>
-    <t>テキスト1</t>
-  </si>
-  <si>
-    <t>テキスト2</t>
-  </si>
-  <si>
-    <t>テキスト3</t>
-  </si>
-  <si>
-    <t>テキスト4</t>
-  </si>
-  <si>
-    <t>テキスト5</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>①ツールA</t>
-  </si>
-  <si>
-    <t>①：テキスト</t>
-  </si>
-  <si>
-    <t>②：テキスト</t>
-  </si>
-  <si>
-    <t>テキスト</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>②ツールA</t>
-  </si>
-  <si>
-    <t>③：テキスト</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>①ツールB
-②ツールC</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>①ツールD
-②ツールE
-③ツールF</t>
-  </si>
-  <si>
-    <t>①②③：テキスト</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>ツールG</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>①〜③：テキスト</t>
-  </si>
-  <si>
-    <t>①②：テキスト</t>
-  </si>
-  <si>
-    <t>①③：テキスト</t>
-  </si>
-  <si>
-    <t>ー</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>①ツールD
-②ツールE
-③ツールF
-④ツールH</t>
-  </si>
-  <si>
-    <t>①②：テキスト1
-③：テキスト2</t>
-  </si>
-  <si>
-    <t>①③：テキスト1
-②：テキスト2</t>
-  </si>
-  <si>
-    <t>①③：テキスト1
-②④：テキスト2</t>
-  </si>
-  <si>
-    <t>①〜③：テキスト1
-④：テキスト2
-⑤：テキスト3</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>①ツールD
-②ツールE
-③ツールF
-④ツールH
-⑤ツールI
-⑥ツールJ
-⑦ツールK
-⑧ツールL
-⑨ツールN</t>
-  </si>
-  <si>
-    <t>①〜③：テキスト1
-④〜⑥：テキスト2</t>
-  </si>
-  <si>
-    <t>①〜③、④：テキスト1
-⑤⑥：テキスト2</t>
-  </si>
-  <si>
-    <t>①〜③、⑤：テキスト1
-④⑥：テキスト2</t>
-  </si>
-  <si>
-    <t>①〜③、④〜⑥：テキスト1
-⑦⑧：テキスト2</t>
-  </si>
-  <si>
-    <t>①〜③、④〜⑥：テキスト
-⑦〜⑨：テキスト</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>①〜③：テキスト1
-④〜⑥：テキスト2
-⑦〜⑨：テキスト2</t>
-  </si>
-  <si>
-    <t>①〜③、④：テキスト1
-⑤⑥：テキスト2
-⑦〜⑨：テキスト3</t>
-  </si>
-  <si>
-    <t>①〜③、⑤：テキスト1
-④、⑦〜⑨：テキスト2
-⑥：テキスト3</t>
-  </si>
-  <si>
-    <t>⑨：テキスト3
-①〜③、④〜⑥：テキスト1
-⑦⑧：テキスト2</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="0" formatCode="General"/>
-    <numFmt numFmtId="59" formatCode="yyyy/m/d"/>
+    <numFmt numFmtId="164" formatCode="yyyy/m/d"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="7">
     <font>
+      <name val="Founders Grotesk"/>
+      <color indexed="8"/>
       <sz val="10"/>
-      <color indexed="8"/>
-      <name val="Founders Grotesk"/>
     </font>
     <font>
+      <name val="ヒラギノ角ゴ ProN W3"/>
+      <color indexed="8"/>
       <sz val="12"/>
-      <color indexed="8"/>
-      <name val="ヒラギノ角ゴ ProN W3"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <color indexed="8"/>
       <sz val="15"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <name val="Founders Grotesk Medium"/>
+      <color indexed="8"/>
       <sz val="12"/>
-      <color indexed="8"/>
-      <name val="Founders Grotesk Medium"/>
     </font>
     <font>
+      <name val="Founders Grotesk"/>
       <b val="1"/>
+      <color indexed="12"/>
       <sz val="10"/>
-      <color indexed="12"/>
-      <name val="Founders Grotesk"/>
     </font>
     <font>
+      <name val="Founders Grotesk Semibold"/>
+      <color indexed="14"/>
       <sz val="10"/>
-      <color indexed="14"/>
-      <name val="Founders Grotesk Semibold"/>
     </font>
     <font>
+      <name val="Founders Grotesk Semibold"/>
+      <color indexed="16"/>
       <sz val="35"/>
-      <color indexed="16"/>
-      <name val="Founders Grotesk Semibold"/>
     </font>
   </fonts>
   <fills count="5">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -497,104 +303,123 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+  <cellXfs count="37">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="59" fontId="4" fillId="3" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="59" fontId="0" fillId="2" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="59" fontId="0" fillId="4" borderId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="59" fontId="0" fillId="2" borderId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="ff000000"/>
@@ -617,144 +442,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>80613</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp>
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="題名1"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="-19050" y="-47292"/>
-          <a:ext cx="9220200" cy="725139"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="12700" cap="flat">
-          <a:noFill/>
-          <a:miter lim="400000"/>
-        </a:ln>
-        <a:effectLst/>
-        <a:extLst>
-          <a:ext uri="{C572A759-6A51-4108-AA02-DFA0A04FC94B}">
-            <ma14:wrappingTextBoxFlag xmlns:ma14="http://schemas.microsoft.com/office/mac/drawingml/2011/main" val="1"/>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="50800" tIns="50800" rIns="50800" bIns="50800" numCol="1" anchor="t">
-          <a:spAutoFit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr marL="0" marR="0" indent="0" algn="l" defTabSz="584200" latinLnBrk="0">
-            <a:lnSpc>
-              <a:spcPct val="60000"/>
-            </a:lnSpc>
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClrTx/>
-            <a:buSzTx/>
-            <a:buFontTx/>
-            <a:buNone/>
-            <a:defRPr b="0" baseline="0" cap="none" i="0" spc="-70" strike="noStrike" sz="3500" u="none">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:uFillTx/>
-              <a:latin typeface="Founders Grotesk Semibold"/>
-              <a:ea typeface="Founders Grotesk Semibold"/>
-              <a:cs typeface="Founders Grotesk Semibold"/>
-              <a:sym typeface="Founders Grotesk Semibold"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:rPr b="0" baseline="0" cap="none" i="0" spc="-70" strike="noStrike" sz="3500" u="none">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:uFillTx/>
-              <a:latin typeface="Founders Grotesk Semibold"/>
-              <a:ea typeface="Founders Grotesk Semibold"/>
-              <a:cs typeface="Founders Grotesk Semibold"/>
-              <a:sym typeface="Founders Grotesk Semibold"/>
-            </a:rPr>
-            <a:t>題名1</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>13970</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1017269</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>13970</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp>
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="線"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="13970"/>
-          <a:ext cx="9145270" cy="1"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="38100" cap="flat">
-          <a:solidFill>
-            <a:schemeClr val="accent4"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="400000"/>
-        </a:ln>
-        <a:effectLst/>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1782,410 +1469,3849 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:I20"/>
-  <sheetFormatPr defaultColWidth="26" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I105"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="26" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0"/>
   <cols>
-    <col min="1" max="1" width="26" style="1" customWidth="1"/>
-    <col min="2" max="7" width="17" style="1" customWidth="1"/>
-    <col min="8" max="8" width="16.6016" style="1" customWidth="1"/>
-    <col min="9" max="9" width="26" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="26" style="1" customWidth="1"/>
+    <col width="26" customWidth="1" style="1" min="1" max="1"/>
+    <col width="17" customWidth="1" style="1" min="2" max="7"/>
+    <col width="16.6016" customWidth="1" style="1" min="8" max="8"/>
+    <col width="26" customWidth="1" style="1" min="9" max="9"/>
+    <col width="26" customWidth="1" style="1" min="10" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="50.75" customHeight="1">
-      <c r="A1" s="2"/>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="4"/>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" t="s" s="5">
-        <v>0</v>
-      </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="7"/>
-    </row>
-    <row r="3" ht="20.15" customHeight="1">
-      <c r="A3" s="8"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="10"/>
-    </row>
-    <row r="4" ht="19.9" customHeight="1">
-      <c r="A4" s="11"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="10"/>
-    </row>
-    <row r="5" ht="20.4" customHeight="1">
-      <c r="A5" t="s" s="13">
-        <v>1</v>
-      </c>
-      <c r="B5" t="s" s="14">
-        <v>2</v>
-      </c>
-      <c r="C5" t="s" s="14">
-        <v>3</v>
-      </c>
-      <c r="D5" t="s" s="14">
-        <v>4</v>
-      </c>
-      <c r="E5" t="s" s="14">
-        <v>5</v>
-      </c>
-      <c r="F5" t="s" s="14">
-        <v>6</v>
-      </c>
-      <c r="G5" t="s" s="14">
-        <v>7</v>
-      </c>
-      <c r="H5" t="s" s="14">
-        <v>8</v>
-      </c>
-      <c r="I5" s="10"/>
-    </row>
-    <row r="6" ht="20.65" customHeight="1">
-      <c r="A6" t="s" s="15">
-        <v>9</v>
-      </c>
-      <c r="B6" s="16">
+    <row r="1" ht="50.75" customHeight="1" s="29">
+      <c r="A1" s="2" t="n"/>
+      <c r="B1" s="3" t="n"/>
+      <c r="C1" s="3" t="n"/>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="4" t="n"/>
+    </row>
+    <row r="2" ht="20" customHeight="1" s="29">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>表</t>
+        </is>
+      </c>
+      <c r="B2" s="30" t="n"/>
+      <c r="C2" s="30" t="n"/>
+      <c r="D2" s="30" t="n"/>
+      <c r="E2" s="30" t="n"/>
+      <c r="F2" s="30" t="n"/>
+      <c r="G2" s="30" t="n"/>
+      <c r="H2" s="30" t="n"/>
+      <c r="I2" s="7" t="n"/>
+    </row>
+    <row r="3" ht="20.15" customHeight="1" s="29">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="9" t="n"/>
+      <c r="C3" s="9" t="n"/>
+      <c r="D3" s="9" t="n"/>
+      <c r="E3" s="9" t="n"/>
+      <c r="F3" s="9" t="n"/>
+      <c r="G3" s="9" t="n"/>
+      <c r="H3" s="9" t="n"/>
+      <c r="I3" s="10" t="n"/>
+    </row>
+    <row r="4" ht="19.9" customHeight="1" s="29">
+      <c r="A4" s="11" t="n"/>
+      <c r="B4" s="31" t="n"/>
+      <c r="C4" s="31" t="n"/>
+      <c r="D4" s="31" t="n"/>
+      <c r="E4" s="31" t="n"/>
+      <c r="F4" s="31" t="n"/>
+      <c r="G4" s="31" t="n"/>
+      <c r="H4" s="31" t="n"/>
+      <c r="I4" s="10" t="n"/>
+    </row>
+    <row r="5" ht="20.4" customHeight="1" s="29">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>処理対象日付</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>ツール一覧</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>テキスト1</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>テキスト2</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>テキスト3</t>
+        </is>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>テキスト4</t>
+        </is>
+      </c>
+      <c r="H5" s="14" t="inlineStr">
+        <is>
+          <t>テキスト5</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="n"/>
+    </row>
+    <row r="6" ht="20.65" customHeight="1" s="29">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B6" s="32" t="n">
         <v>46304</v>
       </c>
-      <c r="C6" t="s" s="17">
-        <v>10</v>
-      </c>
-      <c r="D6" t="s" s="17">
-        <v>11</v>
-      </c>
-      <c r="E6" t="s" s="17">
-        <v>12</v>
-      </c>
-      <c r="F6" s="18"/>
-      <c r="G6" t="s" s="17">
-        <v>11</v>
-      </c>
-      <c r="H6" t="s" s="17">
-        <v>13</v>
-      </c>
-      <c r="I6" s="10"/>
-    </row>
-    <row r="7" ht="20.4" customHeight="1">
-      <c r="A7" t="s" s="19">
-        <v>14</v>
-      </c>
-      <c r="B7" s="20">
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>①ツールA</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>①：テキスト</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>②：テキスト</t>
+        </is>
+      </c>
+      <c r="F6" s="18" t="n"/>
+      <c r="G6" s="17" t="inlineStr">
+        <is>
+          <t>①：テキスト</t>
+        </is>
+      </c>
+      <c r="H6" s="17" t="inlineStr">
+        <is>
+          <t>テキスト</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="n"/>
+    </row>
+    <row r="7" ht="20.4" customHeight="1" s="29">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B7" s="33" t="n">
         <v>46304</v>
       </c>
-      <c r="C7" t="s" s="21">
-        <v>15</v>
-      </c>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-      <c r="F7" t="s" s="21">
-        <v>12</v>
-      </c>
-      <c r="G7" t="s" s="21">
-        <v>11</v>
-      </c>
-      <c r="H7" t="s" s="21">
-        <v>16</v>
-      </c>
-      <c r="I7" s="10"/>
-    </row>
-    <row r="8" ht="37.3" customHeight="1">
-      <c r="A8" t="s" s="19">
-        <v>17</v>
-      </c>
-      <c r="B8" s="23">
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>②ツールA</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="n"/>
+      <c r="E7" s="22" t="n"/>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>②：テキスト</t>
+        </is>
+      </c>
+      <c r="G7" s="21" t="inlineStr">
+        <is>
+          <t>①：テキスト</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t>③：テキスト</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="n"/>
+    </row>
+    <row r="8" ht="37.3" customHeight="1" s="29">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B8" s="34" t="n">
         <v>46305</v>
       </c>
-      <c r="C8" t="s" s="24">
-        <v>18</v>
-      </c>
-      <c r="D8" t="s" s="24">
-        <v>11</v>
-      </c>
-      <c r="E8" t="s" s="24">
-        <v>13</v>
-      </c>
-      <c r="F8" t="s" s="24">
-        <v>12</v>
-      </c>
-      <c r="G8" t="s" s="24">
-        <v>16</v>
-      </c>
-      <c r="H8" s="25"/>
-      <c r="I8" s="10"/>
-    </row>
-    <row r="9" ht="54.2" customHeight="1">
-      <c r="A9" t="s" s="19">
-        <v>19</v>
-      </c>
-      <c r="B9" s="20">
+      <c r="C8" s="24" t="inlineStr">
+        <is>
+          <t>①ツールB
+②ツールC</t>
+        </is>
+      </c>
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>①：テキスト</t>
+        </is>
+      </c>
+      <c r="E8" s="24" t="inlineStr">
+        <is>
+          <t>テキスト</t>
+        </is>
+      </c>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>②：テキスト</t>
+        </is>
+      </c>
+      <c r="G8" s="24" t="inlineStr">
+        <is>
+          <t>③：テキスト</t>
+        </is>
+      </c>
+      <c r="H8" s="25" t="n"/>
+      <c r="I8" s="10" t="n"/>
+    </row>
+    <row r="9" ht="54.2" customHeight="1" s="29">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B9" s="33" t="n">
         <v>46306</v>
       </c>
-      <c r="C9" t="s" s="21">
-        <v>20</v>
-      </c>
-      <c r="D9" t="s" s="21">
-        <v>11</v>
-      </c>
-      <c r="E9" t="s" s="21">
-        <v>13</v>
-      </c>
-      <c r="F9" t="s" s="21">
-        <v>12</v>
-      </c>
-      <c r="G9" t="s" s="21">
-        <v>16</v>
-      </c>
-      <c r="H9" t="s" s="21">
-        <v>21</v>
-      </c>
-      <c r="I9" s="10"/>
-    </row>
-    <row r="10" ht="20.4" customHeight="1">
-      <c r="A10" t="s" s="19">
-        <v>22</v>
-      </c>
-      <c r="B10" s="23">
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>①ツールD
+②ツールE
+③ツールF</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>①：テキスト</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>テキスト</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>②：テキスト</t>
+        </is>
+      </c>
+      <c r="G9" s="21" t="inlineStr">
+        <is>
+          <t>③：テキスト</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>①②③：テキスト</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="n"/>
+    </row>
+    <row r="10" ht="20.4" customHeight="1" s="29">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B10" s="34" t="n">
         <v>46307</v>
       </c>
-      <c r="C10" t="s" s="24">
-        <v>23</v>
-      </c>
-      <c r="D10" t="s" s="24">
-        <v>11</v>
-      </c>
-      <c r="E10" t="s" s="24">
-        <v>12</v>
-      </c>
-      <c r="F10" t="s" s="24">
-        <v>16</v>
-      </c>
-      <c r="G10" t="s" s="24">
-        <v>13</v>
-      </c>
-      <c r="H10" s="25"/>
-      <c r="I10" s="10"/>
-    </row>
-    <row r="11" ht="54.2" customHeight="1">
-      <c r="A11" t="s" s="19">
-        <v>24</v>
-      </c>
-      <c r="B11" s="20">
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>ツールG</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>①：テキスト</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="inlineStr">
+        <is>
+          <t>②：テキスト</t>
+        </is>
+      </c>
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>③：テキスト</t>
+        </is>
+      </c>
+      <c r="G10" s="24" t="inlineStr">
+        <is>
+          <t>テキスト</t>
+        </is>
+      </c>
+      <c r="H10" s="25" t="n"/>
+      <c r="I10" s="10" t="n"/>
+    </row>
+    <row r="11" ht="54.2" customHeight="1" s="29">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B11" s="33" t="n">
         <v>46307</v>
       </c>
-      <c r="C11" t="s" s="21">
-        <v>20</v>
-      </c>
-      <c r="D11" t="s" s="21">
-        <v>25</v>
-      </c>
-      <c r="E11" t="s" s="21">
-        <v>26</v>
-      </c>
-      <c r="F11" t="s" s="21">
-        <v>27</v>
-      </c>
-      <c r="G11" t="s" s="21">
-        <v>13</v>
-      </c>
-      <c r="H11" t="s" s="21">
-        <v>28</v>
-      </c>
-      <c r="I11" s="10"/>
-    </row>
-    <row r="12" ht="71.1" customHeight="1">
-      <c r="A12" t="s" s="19">
-        <v>29</v>
-      </c>
-      <c r="B12" s="23">
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>①ツールD
+②ツールE
+③ツールF</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>①〜③：テキスト</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>①②：テキスト</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>①③：テキスト</t>
+        </is>
+      </c>
+      <c r="G11" s="21" t="inlineStr">
+        <is>
+          <t>テキスト</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="71.09999999999999" customHeight="1" s="29">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B12" s="34" t="n">
         <v>46308</v>
       </c>
-      <c r="C12" t="s" s="24">
-        <v>30</v>
-      </c>
-      <c r="D12" t="s" s="24">
-        <v>25</v>
-      </c>
-      <c r="E12" t="s" s="24">
-        <v>31</v>
-      </c>
-      <c r="F12" t="s" s="24">
-        <v>32</v>
-      </c>
-      <c r="G12" t="s" s="24">
-        <v>33</v>
-      </c>
-      <c r="H12" t="s" s="24">
-        <v>34</v>
-      </c>
-      <c r="I12" s="10"/>
-    </row>
-    <row r="13" ht="155.6" customHeight="1">
-      <c r="A13" t="s" s="19">
-        <v>35</v>
-      </c>
-      <c r="B13" s="20">
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>①ツールD
+②ツールE
+③ツールF
+④ツールH</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>①〜③：テキスト</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>①②：テキスト1
+③：テキスト2</t>
+        </is>
+      </c>
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>①③：テキスト1
+②：テキスト2</t>
+        </is>
+      </c>
+      <c r="G12" s="24" t="inlineStr">
+        <is>
+          <t>①③：テキスト1
+②④：テキスト2</t>
+        </is>
+      </c>
+      <c r="H12" s="24" t="inlineStr">
+        <is>
+          <t>①〜③：テキスト1
+④：テキスト2
+⑤：テキスト3</t>
+        </is>
+      </c>
+      <c r="I12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="155.6" customHeight="1" s="29">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B13" s="33" t="n">
         <v>46308</v>
       </c>
-      <c r="C13" t="s" s="21">
-        <v>36</v>
-      </c>
-      <c r="D13" t="s" s="21">
-        <v>37</v>
-      </c>
-      <c r="E13" t="s" s="21">
-        <v>38</v>
-      </c>
-      <c r="F13" t="s" s="21">
-        <v>39</v>
-      </c>
-      <c r="G13" t="s" s="21">
-        <v>40</v>
-      </c>
-      <c r="H13" t="s" s="21">
-        <v>41</v>
-      </c>
-      <c r="I13" s="10"/>
-    </row>
-    <row r="14" ht="155.6" customHeight="1">
-      <c r="A14" t="s" s="19">
-        <v>42</v>
-      </c>
-      <c r="B14" s="23">
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>①ツールD
+②ツールE
+③ツールF
+④ツールH
+⑤ツールI
+⑥ツールJ
+⑦ツールK
+⑧ツールL
+⑨ツールN</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>①〜③：テキスト1
+④〜⑥：テキスト2</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>①〜③、④：テキスト1
+⑤⑥：テキスト2</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t>①〜③、⑤：テキスト1
+④⑥：テキスト2</t>
+        </is>
+      </c>
+      <c r="G13" s="21" t="inlineStr">
+        <is>
+          <t>①〜③、④〜⑥：テキスト1
+⑦⑧：テキスト2</t>
+        </is>
+      </c>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t>①〜③、④〜⑥：テキスト
+⑦〜⑨：テキスト</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="n"/>
+    </row>
+    <row r="14" ht="155.6" customHeight="1" s="29">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B14" s="34" t="n">
         <v>46308</v>
       </c>
-      <c r="C14" t="s" s="24">
-        <v>36</v>
-      </c>
-      <c r="D14" t="s" s="24">
-        <v>43</v>
-      </c>
-      <c r="E14" t="s" s="24">
-        <v>44</v>
-      </c>
-      <c r="F14" t="s" s="24">
-        <v>45</v>
-      </c>
-      <c r="G14" t="s" s="24">
-        <v>46</v>
-      </c>
-      <c r="H14" t="s" s="24">
-        <v>41</v>
-      </c>
-      <c r="I14" s="10"/>
-    </row>
-    <row r="15" ht="20.4" customHeight="1">
-      <c r="A15" t="s" s="19">
-        <v>47</v>
-      </c>
-      <c r="B15" s="26"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22"/>
-      <c r="I15" s="10"/>
-    </row>
-    <row r="16" ht="20.4" customHeight="1">
-      <c r="A16" t="s" s="19">
-        <v>48</v>
-      </c>
-      <c r="B16" s="27"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="25"/>
-      <c r="I16" s="10"/>
-    </row>
-    <row r="17" ht="20.4" customHeight="1">
-      <c r="A17" t="s" s="19">
-        <v>49</v>
-      </c>
-      <c r="B17" s="26"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
-      <c r="H17" s="22"/>
-      <c r="I17" s="10"/>
-    </row>
-    <row r="18" ht="20.4" customHeight="1">
-      <c r="A18" t="s" s="19">
-        <v>50</v>
-      </c>
-      <c r="B18" s="27"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="25"/>
-      <c r="H18" s="25"/>
-      <c r="I18" s="10"/>
-    </row>
-    <row r="19" ht="20.4" customHeight="1">
-      <c r="A19" t="s" s="19">
-        <v>51</v>
-      </c>
-      <c r="B19" s="26"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="22"/>
-      <c r="H19" s="22"/>
-      <c r="I19" s="10"/>
-    </row>
-    <row r="20" ht="20.4" customHeight="1">
-      <c r="A20" t="s" s="19">
-        <v>52</v>
-      </c>
-      <c r="B20" s="27"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="25"/>
-      <c r="H20" s="25"/>
-      <c r="I20" s="28"/>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>①ツールD
+②ツールE
+③ツールF
+④ツールH
+⑤ツールI
+⑥ツールJ
+⑦ツールK
+⑧ツールL
+⑨ツールN</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>①〜③：テキスト1
+④〜⑥：テキスト2
+⑦〜⑨：テキスト2</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="inlineStr">
+        <is>
+          <t>①〜③、④：テキスト1
+⑤⑥：テキスト2
+⑦〜⑨：テキスト3</t>
+        </is>
+      </c>
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>①〜③、⑤：テキスト1
+④、⑦〜⑨：テキスト2
+⑥：テキスト3</t>
+        </is>
+      </c>
+      <c r="G14" s="24" t="inlineStr">
+        <is>
+          <t>⑨：テキスト3
+①〜③、④〜⑥：テキスト1
+⑦⑧：テキスト2</t>
+        </is>
+      </c>
+      <c r="H14" s="24" t="inlineStr">
+        <is>
+          <t>①〜③、④〜⑥：テキスト
+⑦〜⑨：テキスト</t>
+        </is>
+      </c>
+      <c r="I14" s="10" t="n"/>
+    </row>
+    <row r="15" ht="20.4" customHeight="1" s="29">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B15" s="35" t="n">
+        <v>46309</v>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>❶ツールP
+❷ツールQ</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>❶〜❷：別字体の範囲</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>①：番号指定A
+②：番号指定B</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>共通テキスト</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="H15" s="22" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="I15" s="10" t="n"/>
+    </row>
+    <row r="16" ht="20.4" customHeight="1" s="29">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B16" s="36" t="n">
+        <v>46310</v>
+      </c>
+      <c r="C16" s="25" t="inlineStr">
+        <is>
+          <t>➊ツールR
+➌ツールS</t>
+        </is>
+      </c>
+      <c r="D16" s="25" t="inlineStr">
+        <is>
+          <t>①③：飛び番号テスト</t>
+        </is>
+      </c>
+      <c r="E16" s="25" t="inlineStr">
+        <is>
+          <t>②：対象外テキスト</t>
+        </is>
+      </c>
+      <c r="F16" s="25" t="inlineStr">
+        <is>
+          <t>①：個別A
+③：個別B</t>
+        </is>
+      </c>
+      <c r="G16" s="25" t="n"/>
+      <c r="H16" s="25" t="inlineStr">
+        <is>
+          <t>共通メモ</t>
+        </is>
+      </c>
+      <c r="I16" s="10" t="n"/>
+    </row>
+    <row r="17" ht="20.4" customHeight="1" s="29">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B17" s="35" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>⑩ツールT
+⑪ツールU</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>⑩〜⑪：二桁番号</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>⑩、⑪：区切り指定</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>⑪：個別テキスト</t>
+        </is>
+      </c>
+      <c r="H17" s="22" t="n"/>
+      <c r="I17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="20.4" customHeight="1" s="29">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B18" s="36" t="n">
+        <v>46312</v>
+      </c>
+      <c r="C18" s="25" t="inlineStr">
+        <is>
+          <t>①ツールV
+③ツールW</t>
+        </is>
+      </c>
+      <c r="D18" s="25" t="inlineStr">
+        <is>
+          <t>①③：対象番号
+②：対象外</t>
+        </is>
+      </c>
+      <c r="E18" s="25" t="inlineStr">
+        <is>
+          <t>共通テキスト</t>
+        </is>
+      </c>
+      <c r="F18" s="25" t="inlineStr"/>
+      <c r="G18" s="25" t="inlineStr">
+        <is>
+          <t>③：個別テキスト</t>
+        </is>
+      </c>
+      <c r="H18" s="25" t="n"/>
+      <c r="I18" s="10" t="n"/>
+    </row>
+    <row r="19" ht="20.4" customHeight="1" s="29">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B19" s="35" t="n">
+        <v>46313</v>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>ツールX</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>⑤：テキストから番号補完</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>共通テキスト</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="n"/>
+      <c r="H19" s="22" t="n"/>
+      <c r="I19" s="10" t="n"/>
+    </row>
+    <row r="20" ht="20.4" customHeight="1" s="29">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B20" s="36" t="n">
+        <v>46314</v>
+      </c>
+      <c r="C20" s="25" t="inlineStr">
+        <is>
+          <t>⑳ツールY
+㉑ツールZ</t>
+        </is>
+      </c>
+      <c r="D20" s="25" t="inlineStr">
+        <is>
+          <t>⑳㉑：20番台</t>
+        </is>
+      </c>
+      <c r="E20" s="25" t="inlineStr">
+        <is>
+          <t>㉑：単独指定</t>
+        </is>
+      </c>
+      <c r="F20" s="25" t="inlineStr">
+        <is>
+          <t>共通テキスト</t>
+        </is>
+      </c>
+      <c r="G20" s="25" t="n"/>
+      <c r="H20" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="I20" s="28" t="n"/>
+    </row>
+    <row r="21" ht="20.4" customHeight="1" s="29">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B21" s="36" t="n">
+        <v>46319</v>
+      </c>
+      <c r="C21" s="25" t="inlineStr">
+        <is>
+          <t>❶別字体ツール</t>
+        </is>
+      </c>
+      <c r="D21" s="25" t="inlineStr">
+        <is>
+          <t>❶：別字体テキスト</t>
+        </is>
+      </c>
+      <c r="E21" s="25" t="inlineStr">
+        <is>
+          <t>共通メモ</t>
+        </is>
+      </c>
+      <c r="F21" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="G21" s="25" t="inlineStr">
+        <is>
+          <t>テキスト</t>
+        </is>
+      </c>
+      <c r="H21" s="25" t="n"/>
+    </row>
+    <row r="22" ht="20.4" customHeight="1" s="29">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B22" s="36" t="n">
+        <v>46320</v>
+      </c>
+      <c r="C22" s="25" t="inlineStr">
+        <is>
+          <t>➀別字体ツール</t>
+        </is>
+      </c>
+      <c r="D22" s="25" t="inlineStr">
+        <is>
+          <t>➀：別字体テキスト</t>
+        </is>
+      </c>
+      <c r="E22" s="25" t="inlineStr">
+        <is>
+          <t>共通メモ</t>
+        </is>
+      </c>
+      <c r="F22" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="G22" s="25" t="inlineStr">
+        <is>
+          <t>テキスト</t>
+        </is>
+      </c>
+      <c r="H22" s="25" t="n"/>
+    </row>
+    <row r="23" ht="20.4" customHeight="1" s="29">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B23" s="36" t="n">
+        <v>46321</v>
+      </c>
+      <c r="C23" s="25" t="inlineStr">
+        <is>
+          <t>➊別字体ツール</t>
+        </is>
+      </c>
+      <c r="D23" s="25" t="inlineStr">
+        <is>
+          <t>➊：別字体テキスト</t>
+        </is>
+      </c>
+      <c r="E23" s="25" t="inlineStr">
+        <is>
+          <t>共通メモ</t>
+        </is>
+      </c>
+      <c r="F23" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="G23" s="25" t="inlineStr">
+        <is>
+          <t>テキスト</t>
+        </is>
+      </c>
+      <c r="H23" s="25" t="n"/>
+    </row>
+    <row r="24" ht="20.4" customHeight="1" s="29">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B24" s="36" t="n">
+        <v>46322</v>
+      </c>
+      <c r="C24" s="25" t="inlineStr">
+        <is>
+          <t>⓵別字体ツール</t>
+        </is>
+      </c>
+      <c r="D24" s="25" t="inlineStr">
+        <is>
+          <t>⓵：別字体テキスト</t>
+        </is>
+      </c>
+      <c r="E24" s="25" t="inlineStr">
+        <is>
+          <t>共通メモ</t>
+        </is>
+      </c>
+      <c r="F24" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="G24" s="25" t="inlineStr">
+        <is>
+          <t>テキスト</t>
+        </is>
+      </c>
+      <c r="H24" s="25" t="n"/>
+    </row>
+    <row r="25" ht="20.4" customHeight="1" s="29">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B25" s="36" t="n">
+        <v>46323</v>
+      </c>
+      <c r="C25" s="25" t="inlineStr">
+        <is>
+          <t>❷別字体ツール</t>
+        </is>
+      </c>
+      <c r="D25" s="25" t="inlineStr">
+        <is>
+          <t>❷：別字体テキスト</t>
+        </is>
+      </c>
+      <c r="E25" s="25" t="inlineStr">
+        <is>
+          <t>共通メモ</t>
+        </is>
+      </c>
+      <c r="F25" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="G25" s="25" t="inlineStr">
+        <is>
+          <t>テキスト</t>
+        </is>
+      </c>
+      <c r="H25" s="25" t="n"/>
+    </row>
+    <row r="26" ht="20.4" customHeight="1" s="29">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B26" s="36" t="n">
+        <v>46324</v>
+      </c>
+      <c r="C26" s="25" t="inlineStr">
+        <is>
+          <t>➁別字体ツール</t>
+        </is>
+      </c>
+      <c r="D26" s="25" t="inlineStr">
+        <is>
+          <t>➁：別字体テキスト</t>
+        </is>
+      </c>
+      <c r="E26" s="25" t="inlineStr">
+        <is>
+          <t>共通メモ</t>
+        </is>
+      </c>
+      <c r="F26" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="G26" s="25" t="inlineStr">
+        <is>
+          <t>テキスト</t>
+        </is>
+      </c>
+      <c r="H26" s="25" t="n"/>
+    </row>
+    <row r="27" ht="20.4" customHeight="1" s="29">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B27" s="36" t="n">
+        <v>46325</v>
+      </c>
+      <c r="C27" s="25" t="inlineStr">
+        <is>
+          <t>➋別字体ツール</t>
+        </is>
+      </c>
+      <c r="D27" s="25" t="inlineStr">
+        <is>
+          <t>➋：別字体テキスト</t>
+        </is>
+      </c>
+      <c r="E27" s="25" t="inlineStr">
+        <is>
+          <t>共通メモ</t>
+        </is>
+      </c>
+      <c r="F27" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="G27" s="25" t="inlineStr">
+        <is>
+          <t>テキスト</t>
+        </is>
+      </c>
+      <c r="H27" s="25" t="n"/>
+    </row>
+    <row r="28" ht="20.4" customHeight="1" s="29">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B28" s="36" t="n">
+        <v>46326</v>
+      </c>
+      <c r="C28" s="25" t="inlineStr">
+        <is>
+          <t>⓶別字体ツール</t>
+        </is>
+      </c>
+      <c r="D28" s="25" t="inlineStr">
+        <is>
+          <t>⓶：別字体テキスト</t>
+        </is>
+      </c>
+      <c r="E28" s="25" t="inlineStr">
+        <is>
+          <t>共通メモ</t>
+        </is>
+      </c>
+      <c r="F28" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="G28" s="25" t="inlineStr">
+        <is>
+          <t>テキスト</t>
+        </is>
+      </c>
+      <c r="H28" s="25" t="n"/>
+    </row>
+    <row r="29" ht="20.4" customHeight="1" s="29">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B29" s="36" t="n">
+        <v>46327</v>
+      </c>
+      <c r="C29" s="25" t="inlineStr">
+        <is>
+          <t>❸別字体ツール</t>
+        </is>
+      </c>
+      <c r="D29" s="25" t="inlineStr">
+        <is>
+          <t>❸：別字体テキスト</t>
+        </is>
+      </c>
+      <c r="E29" s="25" t="inlineStr">
+        <is>
+          <t>共通メモ</t>
+        </is>
+      </c>
+      <c r="F29" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="G29" s="25" t="inlineStr">
+        <is>
+          <t>テキスト</t>
+        </is>
+      </c>
+      <c r="H29" s="25" t="n"/>
+    </row>
+    <row r="30" ht="20.4" customHeight="1" s="29">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B30" s="36" t="n">
+        <v>46328</v>
+      </c>
+      <c r="C30" s="25" t="inlineStr">
+        <is>
+          <t>➂別字体ツール</t>
+        </is>
+      </c>
+      <c r="D30" s="25" t="inlineStr">
+        <is>
+          <t>➂：別字体テキスト</t>
+        </is>
+      </c>
+      <c r="E30" s="25" t="inlineStr">
+        <is>
+          <t>共通メモ</t>
+        </is>
+      </c>
+      <c r="F30" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="G30" s="25" t="inlineStr">
+        <is>
+          <t>テキスト</t>
+        </is>
+      </c>
+      <c r="H30" s="25" t="n"/>
+    </row>
+    <row r="31" ht="20.4" customHeight="1" s="29">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B31" s="36" t="n">
+        <v>46329</v>
+      </c>
+      <c r="C31" s="25" t="inlineStr">
+        <is>
+          <t>①ツールA
+②ツールB
+③ツールC
+④ツールD</t>
+        </is>
+      </c>
+      <c r="D31" s="25" t="inlineStr">
+        <is>
+          <t>①〜③：範囲・リスト試験</t>
+        </is>
+      </c>
+      <c r="E31" s="25" t="inlineStr">
+        <is>
+          <t>④：番号④</t>
+        </is>
+      </c>
+      <c r="F31" s="25" t="inlineStr">
+        <is>
+          <t>共通文</t>
+        </is>
+      </c>
+      <c r="G31" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="H31" s="25" t="n"/>
+    </row>
+    <row r="32" ht="20.4" customHeight="1" s="29">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B32" s="36" t="n">
+        <v>46330</v>
+      </c>
+      <c r="C32" s="25" t="inlineStr">
+        <is>
+          <t>①ツールA
+②ツールB
+③ツールC
+④ツールD</t>
+        </is>
+      </c>
+      <c r="D32" s="25" t="inlineStr">
+        <is>
+          <t>①-③：範囲・リスト試験</t>
+        </is>
+      </c>
+      <c r="E32" s="25" t="inlineStr">
+        <is>
+          <t>④：番号④</t>
+        </is>
+      </c>
+      <c r="F32" s="25" t="inlineStr">
+        <is>
+          <t>共通文</t>
+        </is>
+      </c>
+      <c r="G32" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="H32" s="25" t="n"/>
+    </row>
+    <row r="33" ht="20.4" customHeight="1" s="29">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B33" s="36" t="n">
+        <v>46331</v>
+      </c>
+      <c r="C33" s="25" t="inlineStr">
+        <is>
+          <t>①ツールA
+②ツールB
+③ツールC
+④ツールD</t>
+        </is>
+      </c>
+      <c r="D33" s="25" t="inlineStr">
+        <is>
+          <t>①~③：範囲・リスト試験</t>
+        </is>
+      </c>
+      <c r="E33" s="25" t="inlineStr">
+        <is>
+          <t>④：番号④</t>
+        </is>
+      </c>
+      <c r="F33" s="25" t="inlineStr">
+        <is>
+          <t>共通文</t>
+        </is>
+      </c>
+      <c r="G33" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="H33" s="25" t="n"/>
+    </row>
+    <row r="34" ht="20.4" customHeight="1" s="29">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B34" s="36" t="n">
+        <v>46332</v>
+      </c>
+      <c r="C34" s="25" t="inlineStr">
+        <is>
+          <t>①ツールA
+②ツールB
+③ツールC
+④ツールD</t>
+        </is>
+      </c>
+      <c r="D34" s="25" t="inlineStr">
+        <is>
+          <t>① 〜 ③：範囲・リスト試験</t>
+        </is>
+      </c>
+      <c r="E34" s="25" t="inlineStr">
+        <is>
+          <t>④：番号④</t>
+        </is>
+      </c>
+      <c r="F34" s="25" t="inlineStr">
+        <is>
+          <t>共通文</t>
+        </is>
+      </c>
+      <c r="G34" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="H34" s="25" t="n"/>
+    </row>
+    <row r="35" ht="20.4" customHeight="1" s="29">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B35" s="36" t="n">
+        <v>46333</v>
+      </c>
+      <c r="C35" s="25" t="inlineStr">
+        <is>
+          <t>①ツールA
+②ツールB
+③ツールC
+④ツールD</t>
+        </is>
+      </c>
+      <c r="D35" s="25" t="inlineStr">
+        <is>
+          <t>①,③：範囲・リスト試験</t>
+        </is>
+      </c>
+      <c r="E35" s="25" t="inlineStr">
+        <is>
+          <t>④：番号④</t>
+        </is>
+      </c>
+      <c r="F35" s="25" t="inlineStr">
+        <is>
+          <t>共通文</t>
+        </is>
+      </c>
+      <c r="G35" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="H35" s="25" t="n"/>
+    </row>
+    <row r="36" ht="20.4" customHeight="1" s="29">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B36" s="36" t="n">
+        <v>46334</v>
+      </c>
+      <c r="C36" s="25" t="inlineStr">
+        <is>
+          <t>①ツールA
+②ツールB
+③ツールC
+④ツールD</t>
+        </is>
+      </c>
+      <c r="D36" s="25" t="inlineStr">
+        <is>
+          <t>①、③：範囲・リスト試験</t>
+        </is>
+      </c>
+      <c r="E36" s="25" t="inlineStr">
+        <is>
+          <t>④：番号④</t>
+        </is>
+      </c>
+      <c r="F36" s="25" t="inlineStr">
+        <is>
+          <t>共通文</t>
+        </is>
+      </c>
+      <c r="G36" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="H36" s="25" t="n"/>
+    </row>
+    <row r="37" ht="20.4" customHeight="1" s="29">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B37" s="36" t="n">
+        <v>46335</v>
+      </c>
+      <c r="C37" s="25" t="inlineStr">
+        <is>
+          <t>①ツールA
+②ツールB
+③ツールC
+④ツールD</t>
+        </is>
+      </c>
+      <c r="D37" s="25" t="inlineStr">
+        <is>
+          <t>①②③：範囲・リスト試験</t>
+        </is>
+      </c>
+      <c r="E37" s="25" t="inlineStr">
+        <is>
+          <t>④：番号④</t>
+        </is>
+      </c>
+      <c r="F37" s="25" t="inlineStr">
+        <is>
+          <t>共通文</t>
+        </is>
+      </c>
+      <c r="G37" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="H37" s="25" t="n"/>
+    </row>
+    <row r="38" ht="20.4" customHeight="1" s="29">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B38" s="36" t="n">
+        <v>46336</v>
+      </c>
+      <c r="C38" s="25" t="inlineStr">
+        <is>
+          <t>①ツールA
+②ツールB
+③ツールC
+④ツールD</t>
+        </is>
+      </c>
+      <c r="D38" s="25" t="inlineStr">
+        <is>
+          <t>①〜②、③：範囲・リスト試験</t>
+        </is>
+      </c>
+      <c r="E38" s="25" t="inlineStr">
+        <is>
+          <t>④：番号④</t>
+        </is>
+      </c>
+      <c r="F38" s="25" t="inlineStr">
+        <is>
+          <t>共通文</t>
+        </is>
+      </c>
+      <c r="G38" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="H38" s="25" t="n"/>
+    </row>
+    <row r="39" ht="20.4" customHeight="1" s="29">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B39" s="36" t="n">
+        <v>46337</v>
+      </c>
+      <c r="C39" s="25" t="inlineStr">
+        <is>
+          <t>①ツールA
+②ツールB
+③ツールC
+④ツールD</t>
+        </is>
+      </c>
+      <c r="D39" s="25" t="inlineStr">
+        <is>
+          <t>②〜④：範囲・リスト試験</t>
+        </is>
+      </c>
+      <c r="E39" s="25" t="inlineStr">
+        <is>
+          <t>④：番号④</t>
+        </is>
+      </c>
+      <c r="F39" s="25" t="inlineStr">
+        <is>
+          <t>共通文</t>
+        </is>
+      </c>
+      <c r="G39" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="H39" s="25" t="n"/>
+    </row>
+    <row r="40" ht="20.4" customHeight="1" s="29">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B40" s="36" t="n">
+        <v>46338</v>
+      </c>
+      <c r="C40" s="25" t="inlineStr">
+        <is>
+          <t>①ツールA
+②ツールB
+③ツールC
+④ツールD</t>
+        </is>
+      </c>
+      <c r="D40" s="25" t="inlineStr">
+        <is>
+          <t>①~④：範囲・リスト試験</t>
+        </is>
+      </c>
+      <c r="E40" s="25" t="inlineStr">
+        <is>
+          <t>④：番号④</t>
+        </is>
+      </c>
+      <c r="F40" s="25" t="inlineStr">
+        <is>
+          <t>共通文</t>
+        </is>
+      </c>
+      <c r="G40" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="H40" s="25" t="n"/>
+    </row>
+    <row r="41" ht="20.4" customHeight="1" s="29">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B41" s="36" t="n">
+        <v>46339</v>
+      </c>
+      <c r="C41" s="25" t="inlineStr">
+        <is>
+          <t>①ツールA
+③ツールC
+⑤ツールE</t>
+        </is>
+      </c>
+      <c r="D41" s="25" t="inlineStr">
+        <is>
+          <t>①③⑤：対象テキスト
+②：対象外テキスト</t>
+        </is>
+      </c>
+      <c r="E41" s="25" t="inlineStr">
+        <is>
+          <t>共通メモ</t>
+        </is>
+      </c>
+      <c r="F41" s="25" t="inlineStr">
+        <is>
+          <t>⑤：個別テキスト</t>
+        </is>
+      </c>
+      <c r="G41" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="H41" s="25" t="n"/>
+    </row>
+    <row r="42" ht="20.4" customHeight="1" s="29">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B42" s="36" t="n">
+        <v>46340</v>
+      </c>
+      <c r="C42" s="25" t="inlineStr">
+        <is>
+          <t>①ツールA
+③ツールC
+⑤ツールE</t>
+        </is>
+      </c>
+      <c r="D42" s="25" t="inlineStr">
+        <is>
+          <t>①③⑤：対象テキスト
+②：対象外テキスト</t>
+        </is>
+      </c>
+      <c r="E42" s="25" t="inlineStr">
+        <is>
+          <t>共通メモ</t>
+        </is>
+      </c>
+      <c r="F42" s="25" t="inlineStr">
+        <is>
+          <t>⑤：個別テキスト</t>
+        </is>
+      </c>
+      <c r="G42" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="H42" s="25" t="n"/>
+    </row>
+    <row r="43" ht="20.4" customHeight="1" s="29">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B43" s="36" t="n">
+        <v>46341</v>
+      </c>
+      <c r="C43" s="25" t="inlineStr">
+        <is>
+          <t>①ツールA
+③ツールC
+⑤ツールE</t>
+        </is>
+      </c>
+      <c r="D43" s="25" t="inlineStr">
+        <is>
+          <t>①③⑤：対象テキスト
+②：対象外テキスト</t>
+        </is>
+      </c>
+      <c r="E43" s="25" t="inlineStr">
+        <is>
+          <t>共通メモ</t>
+        </is>
+      </c>
+      <c r="F43" s="25" t="inlineStr">
+        <is>
+          <t>⑤：個別テキスト</t>
+        </is>
+      </c>
+      <c r="G43" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="H43" s="25" t="n"/>
+    </row>
+    <row r="44" ht="20.4" customHeight="1" s="29">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B44" s="36" t="n">
+        <v>46342</v>
+      </c>
+      <c r="C44" s="25" t="inlineStr">
+        <is>
+          <t>①ツールA
+③ツールC
+⑤ツールE</t>
+        </is>
+      </c>
+      <c r="D44" s="25" t="inlineStr">
+        <is>
+          <t>①③⑤：対象テキスト
+②：対象外テキスト</t>
+        </is>
+      </c>
+      <c r="E44" s="25" t="inlineStr">
+        <is>
+          <t>共通メモ</t>
+        </is>
+      </c>
+      <c r="F44" s="25" t="inlineStr">
+        <is>
+          <t>⑤：個別テキスト</t>
+        </is>
+      </c>
+      <c r="G44" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="H44" s="25" t="n"/>
+    </row>
+    <row r="45" ht="20.4" customHeight="1" s="29">
+      <c r="A45" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B45" s="36" t="n">
+        <v>46343</v>
+      </c>
+      <c r="C45" s="25" t="inlineStr">
+        <is>
+          <t>①ツールA
+③ツールC
+⑤ツールE</t>
+        </is>
+      </c>
+      <c r="D45" s="25" t="inlineStr">
+        <is>
+          <t>①③⑤：対象テキスト
+②：対象外テキスト</t>
+        </is>
+      </c>
+      <c r="E45" s="25" t="inlineStr">
+        <is>
+          <t>共通メモ</t>
+        </is>
+      </c>
+      <c r="F45" s="25" t="inlineStr">
+        <is>
+          <t>⑤：個別テキスト</t>
+        </is>
+      </c>
+      <c r="G45" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="H45" s="25" t="n"/>
+    </row>
+    <row r="46" ht="20.4" customHeight="1" s="29">
+      <c r="A46" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B46" s="36" t="n">
+        <v>46344</v>
+      </c>
+      <c r="C46" s="25" t="inlineStr">
+        <is>
+          <t>①ツールA
+③ツールC
+⑤ツールE</t>
+        </is>
+      </c>
+      <c r="D46" s="25" t="inlineStr">
+        <is>
+          <t>①③⑤：対象テキスト
+②：対象外テキスト</t>
+        </is>
+      </c>
+      <c r="E46" s="25" t="inlineStr">
+        <is>
+          <t>共通メモ</t>
+        </is>
+      </c>
+      <c r="F46" s="25" t="inlineStr">
+        <is>
+          <t>⑤：個別テキスト</t>
+        </is>
+      </c>
+      <c r="G46" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="H46" s="25" t="n"/>
+    </row>
+    <row r="47" ht="20.4" customHeight="1" s="29">
+      <c r="A47" s="19" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B47" s="36" t="n">
+        <v>46345</v>
+      </c>
+      <c r="C47" s="25" t="inlineStr">
+        <is>
+          <t>①ツールA
+③ツールC
+⑤ツールE</t>
+        </is>
+      </c>
+      <c r="D47" s="25" t="inlineStr">
+        <is>
+          <t>①③⑤：対象テキスト
+②：対象外テキスト</t>
+        </is>
+      </c>
+      <c r="E47" s="25" t="inlineStr">
+        <is>
+          <t>共通メモ</t>
+        </is>
+      </c>
+      <c r="F47" s="25" t="inlineStr">
+        <is>
+          <t>⑤：個別テキスト</t>
+        </is>
+      </c>
+      <c r="G47" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="H47" s="25" t="n"/>
+    </row>
+    <row r="48" ht="20.4" customHeight="1" s="29">
+      <c r="A48" s="19" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B48" s="36" t="n">
+        <v>46346</v>
+      </c>
+      <c r="C48" s="25" t="inlineStr">
+        <is>
+          <t>①ツールA
+③ツールC
+⑤ツールE</t>
+        </is>
+      </c>
+      <c r="D48" s="25" t="inlineStr">
+        <is>
+          <t>①③⑤：対象テキスト
+②：対象外テキスト</t>
+        </is>
+      </c>
+      <c r="E48" s="25" t="inlineStr">
+        <is>
+          <t>共通メモ</t>
+        </is>
+      </c>
+      <c r="F48" s="25" t="inlineStr">
+        <is>
+          <t>⑤：個別テキスト</t>
+        </is>
+      </c>
+      <c r="G48" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="H48" s="25" t="n"/>
+    </row>
+    <row r="49" ht="20.4" customHeight="1" s="29">
+      <c r="A49" s="19" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B49" s="36" t="n">
+        <v>46347</v>
+      </c>
+      <c r="C49" s="25" t="inlineStr">
+        <is>
+          <t>①ツールA
+③ツールC
+⑤ツールE</t>
+        </is>
+      </c>
+      <c r="D49" s="25" t="inlineStr">
+        <is>
+          <t>①③⑤：対象テキスト
+②：対象外テキスト</t>
+        </is>
+      </c>
+      <c r="E49" s="25" t="inlineStr">
+        <is>
+          <t>共通メモ</t>
+        </is>
+      </c>
+      <c r="F49" s="25" t="inlineStr">
+        <is>
+          <t>⑤：個別テキスト</t>
+        </is>
+      </c>
+      <c r="G49" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="H49" s="25" t="n"/>
+    </row>
+    <row r="50" ht="20.4" customHeight="1" s="29">
+      <c r="A50" s="19" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B50" s="36" t="n">
+        <v>46348</v>
+      </c>
+      <c r="C50" s="25" t="inlineStr">
+        <is>
+          <t>①ツールA
+③ツールC
+⑤ツールE</t>
+        </is>
+      </c>
+      <c r="D50" s="25" t="inlineStr">
+        <is>
+          <t>①③⑤：対象テキスト
+②：対象外テキスト</t>
+        </is>
+      </c>
+      <c r="E50" s="25" t="inlineStr">
+        <is>
+          <t>共通メモ</t>
+        </is>
+      </c>
+      <c r="F50" s="25" t="inlineStr">
+        <is>
+          <t>⑤：個別テキスト</t>
+        </is>
+      </c>
+      <c r="G50" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="H50" s="25" t="n"/>
+    </row>
+    <row r="51" ht="20.4" customHeight="1" s="29">
+      <c r="A51" s="19" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B51" s="36" t="n">
+        <v>46349</v>
+      </c>
+      <c r="C51" s="25" t="inlineStr">
+        <is>
+          <t>①ツールA
+②ツールB
+③ツールC</t>
+        </is>
+      </c>
+      <c r="D51" s="25" t="inlineStr">
+        <is>
+          <t>①：専用-46
+共通-46</t>
+        </is>
+      </c>
+      <c r="E51" s="25" t="inlineStr">
+        <is>
+          <t>②：専用B</t>
+        </is>
+      </c>
+      <c r="F51" s="25" t="inlineStr">
+        <is>
+          <t>共通だけ</t>
+        </is>
+      </c>
+      <c r="G51" s="25" t="inlineStr">
+        <is>
+          <t>③：専用C</t>
+        </is>
+      </c>
+      <c r="H51" s="25" t="n"/>
+    </row>
+    <row r="52" ht="20.4" customHeight="1" s="29">
+      <c r="A52" s="19" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="B52" s="36" t="n">
+        <v>46350</v>
+      </c>
+      <c r="C52" s="25" t="inlineStr">
+        <is>
+          <t>①ツールA
+②ツールB
+③ツールC</t>
+        </is>
+      </c>
+      <c r="D52" s="25" t="inlineStr">
+        <is>
+          <t>①：専用-47
+共通-47</t>
+        </is>
+      </c>
+      <c r="E52" s="25" t="inlineStr">
+        <is>
+          <t>②：専用B</t>
+        </is>
+      </c>
+      <c r="F52" s="25" t="inlineStr">
+        <is>
+          <t>共通だけ</t>
+        </is>
+      </c>
+      <c r="G52" s="25" t="inlineStr">
+        <is>
+          <t>③：専用C</t>
+        </is>
+      </c>
+      <c r="H52" s="25" t="n"/>
+    </row>
+    <row r="53" ht="20.4" customHeight="1" s="29">
+      <c r="A53" s="19" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B53" s="36" t="n">
+        <v>46351</v>
+      </c>
+      <c r="C53" s="25" t="inlineStr">
+        <is>
+          <t>①ツールA
+②ツールB
+③ツールC</t>
+        </is>
+      </c>
+      <c r="D53" s="25" t="inlineStr">
+        <is>
+          <t>①：専用-48
+共通-48</t>
+        </is>
+      </c>
+      <c r="E53" s="25" t="inlineStr">
+        <is>
+          <t>②：専用B</t>
+        </is>
+      </c>
+      <c r="F53" s="25" t="inlineStr">
+        <is>
+          <t>共通だけ</t>
+        </is>
+      </c>
+      <c r="G53" s="25" t="inlineStr">
+        <is>
+          <t>③：専用C</t>
+        </is>
+      </c>
+      <c r="H53" s="25" t="n"/>
+    </row>
+    <row r="54" ht="20.4" customHeight="1" s="29">
+      <c r="A54" s="19" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="B54" s="36" t="n">
+        <v>46352</v>
+      </c>
+      <c r="C54" s="25" t="inlineStr">
+        <is>
+          <t>①ツールA
+②ツールB
+③ツールC</t>
+        </is>
+      </c>
+      <c r="D54" s="25" t="inlineStr">
+        <is>
+          <t>①：専用-49
+共通-49</t>
+        </is>
+      </c>
+      <c r="E54" s="25" t="inlineStr">
+        <is>
+          <t>②：専用B</t>
+        </is>
+      </c>
+      <c r="F54" s="25" t="inlineStr">
+        <is>
+          <t>共通だけ</t>
+        </is>
+      </c>
+      <c r="G54" s="25" t="inlineStr">
+        <is>
+          <t>③：専用C</t>
+        </is>
+      </c>
+      <c r="H54" s="25" t="n"/>
+    </row>
+    <row r="55" ht="20.4" customHeight="1" s="29">
+      <c r="A55" s="19" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="B55" s="36" t="n">
+        <v>46353</v>
+      </c>
+      <c r="C55" s="25" t="inlineStr">
+        <is>
+          <t>①ツールA
+②ツールB
+③ツールC</t>
+        </is>
+      </c>
+      <c r="D55" s="25" t="inlineStr">
+        <is>
+          <t>①：専用-50
+共通-50</t>
+        </is>
+      </c>
+      <c r="E55" s="25" t="inlineStr">
+        <is>
+          <t>②：専用B</t>
+        </is>
+      </c>
+      <c r="F55" s="25" t="inlineStr">
+        <is>
+          <t>共通だけ</t>
+        </is>
+      </c>
+      <c r="G55" s="25" t="inlineStr">
+        <is>
+          <t>③：専用C</t>
+        </is>
+      </c>
+      <c r="H55" s="25" t="n"/>
+    </row>
+    <row r="56" ht="20.4" customHeight="1" s="29">
+      <c r="A56" s="19" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B56" s="36" t="n">
+        <v>46354</v>
+      </c>
+      <c r="C56" s="25" t="inlineStr">
+        <is>
+          <t>①ツールA
+②ツールB
+③ツールC</t>
+        </is>
+      </c>
+      <c r="D56" s="25" t="inlineStr">
+        <is>
+          <t>①：専用-51
+共通-51</t>
+        </is>
+      </c>
+      <c r="E56" s="25" t="inlineStr">
+        <is>
+          <t>②：専用B</t>
+        </is>
+      </c>
+      <c r="F56" s="25" t="inlineStr">
+        <is>
+          <t>共通だけ</t>
+        </is>
+      </c>
+      <c r="G56" s="25" t="inlineStr">
+        <is>
+          <t>③：専用C</t>
+        </is>
+      </c>
+      <c r="H56" s="25" t="n"/>
+    </row>
+    <row r="57" ht="20.4" customHeight="1" s="29">
+      <c r="A57" s="19" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B57" s="36" t="n">
+        <v>46355</v>
+      </c>
+      <c r="C57" s="25" t="inlineStr">
+        <is>
+          <t>①ツールA
+②ツールB
+③ツールC</t>
+        </is>
+      </c>
+      <c r="D57" s="25" t="inlineStr">
+        <is>
+          <t>①：専用-52
+共通-52</t>
+        </is>
+      </c>
+      <c r="E57" s="25" t="inlineStr">
+        <is>
+          <t>②：専用B</t>
+        </is>
+      </c>
+      <c r="F57" s="25" t="inlineStr">
+        <is>
+          <t>共通だけ</t>
+        </is>
+      </c>
+      <c r="G57" s="25" t="inlineStr">
+        <is>
+          <t>③：専用C</t>
+        </is>
+      </c>
+      <c r="H57" s="25" t="n"/>
+    </row>
+    <row r="58" ht="20.4" customHeight="1" s="29">
+      <c r="A58" s="19" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="B58" s="36" t="n">
+        <v>46356</v>
+      </c>
+      <c r="C58" s="25" t="inlineStr">
+        <is>
+          <t>①ツールA
+②ツールB
+③ツールC</t>
+        </is>
+      </c>
+      <c r="D58" s="25" t="inlineStr">
+        <is>
+          <t>①：専用-53
+共通-53</t>
+        </is>
+      </c>
+      <c r="E58" s="25" t="inlineStr">
+        <is>
+          <t>②：専用B</t>
+        </is>
+      </c>
+      <c r="F58" s="25" t="inlineStr">
+        <is>
+          <t>共通だけ</t>
+        </is>
+      </c>
+      <c r="G58" s="25" t="inlineStr">
+        <is>
+          <t>③：専用C</t>
+        </is>
+      </c>
+      <c r="H58" s="25" t="n"/>
+    </row>
+    <row r="59" ht="20.4" customHeight="1" s="29">
+      <c r="A59" s="19" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="B59" s="36" t="n">
+        <v>46357</v>
+      </c>
+      <c r="C59" s="25" t="inlineStr">
+        <is>
+          <t>①ツールA
+②ツールB
+③ツールC</t>
+        </is>
+      </c>
+      <c r="D59" s="25" t="inlineStr">
+        <is>
+          <t>①：専用-54
+共通-54</t>
+        </is>
+      </c>
+      <c r="E59" s="25" t="inlineStr">
+        <is>
+          <t>②：専用B</t>
+        </is>
+      </c>
+      <c r="F59" s="25" t="inlineStr">
+        <is>
+          <t>共通だけ</t>
+        </is>
+      </c>
+      <c r="G59" s="25" t="inlineStr">
+        <is>
+          <t>③：専用C</t>
+        </is>
+      </c>
+      <c r="H59" s="25" t="n"/>
+    </row>
+    <row r="60" ht="20.4" customHeight="1" s="29">
+      <c r="A60" s="19" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="B60" s="36" t="n">
+        <v>46358</v>
+      </c>
+      <c r="C60" s="25" t="inlineStr">
+        <is>
+          <t>①ツールA
+②ツールB
+③ツールC</t>
+        </is>
+      </c>
+      <c r="D60" s="25" t="inlineStr">
+        <is>
+          <t>①：専用-55
+共通-55</t>
+        </is>
+      </c>
+      <c r="E60" s="25" t="inlineStr">
+        <is>
+          <t>②：専用B</t>
+        </is>
+      </c>
+      <c r="F60" s="25" t="inlineStr">
+        <is>
+          <t>共通だけ</t>
+        </is>
+      </c>
+      <c r="G60" s="25" t="inlineStr">
+        <is>
+          <t>③：専用C</t>
+        </is>
+      </c>
+      <c r="H60" s="25" t="n"/>
+    </row>
+    <row r="61" ht="20.4" customHeight="1" s="29">
+      <c r="A61" s="19" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="B61" s="36" t="n">
+        <v>46359</v>
+      </c>
+      <c r="C61" s="25" t="inlineStr">
+        <is>
+          <t>番号なしツール-56</t>
+        </is>
+      </c>
+      <c r="D61" s="25" t="inlineStr">
+        <is>
+          <t>①：補完A-56</t>
+        </is>
+      </c>
+      <c r="E61" s="25" t="inlineStr">
+        <is>
+          <t>③：補完C</t>
+        </is>
+      </c>
+      <c r="F61" s="25" t="inlineStr">
+        <is>
+          <t>共通テキスト</t>
+        </is>
+      </c>
+      <c r="G61" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="H61" s="25" t="n"/>
+    </row>
+    <row r="62" ht="20.4" customHeight="1" s="29">
+      <c r="A62" s="19" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="B62" s="36" t="n">
+        <v>46360</v>
+      </c>
+      <c r="C62" s="25" t="inlineStr">
+        <is>
+          <t>番号なしツール-57</t>
+        </is>
+      </c>
+      <c r="D62" s="25" t="inlineStr">
+        <is>
+          <t>①：補完A-57</t>
+        </is>
+      </c>
+      <c r="E62" s="25" t="inlineStr">
+        <is>
+          <t>③：補完C</t>
+        </is>
+      </c>
+      <c r="F62" s="25" t="inlineStr">
+        <is>
+          <t>共通テキスト</t>
+        </is>
+      </c>
+      <c r="G62" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="H62" s="25" t="n"/>
+    </row>
+    <row r="63" ht="20.4" customHeight="1" s="29">
+      <c r="A63" s="19" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="B63" s="36" t="n">
+        <v>46361</v>
+      </c>
+      <c r="C63" s="25" t="inlineStr">
+        <is>
+          <t>番号なしツール-58</t>
+        </is>
+      </c>
+      <c r="D63" s="25" t="inlineStr">
+        <is>
+          <t>①：補完A-58</t>
+        </is>
+      </c>
+      <c r="E63" s="25" t="inlineStr">
+        <is>
+          <t>③：補完C</t>
+        </is>
+      </c>
+      <c r="F63" s="25" t="inlineStr">
+        <is>
+          <t>共通テキスト</t>
+        </is>
+      </c>
+      <c r="G63" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="H63" s="25" t="n"/>
+    </row>
+    <row r="64" ht="20.4" customHeight="1" s="29">
+      <c r="A64" s="19" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="B64" s="36" t="n">
+        <v>46362</v>
+      </c>
+      <c r="C64" s="25" t="inlineStr">
+        <is>
+          <t>番号なしツール-59</t>
+        </is>
+      </c>
+      <c r="D64" s="25" t="inlineStr">
+        <is>
+          <t>①：補完A-59</t>
+        </is>
+      </c>
+      <c r="E64" s="25" t="inlineStr">
+        <is>
+          <t>③：補完C</t>
+        </is>
+      </c>
+      <c r="F64" s="25" t="inlineStr">
+        <is>
+          <t>共通テキスト</t>
+        </is>
+      </c>
+      <c r="G64" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="H64" s="25" t="n"/>
+    </row>
+    <row r="65" ht="20.4" customHeight="1" s="29">
+      <c r="A65" s="19" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B65" s="36" t="n">
+        <v>46363</v>
+      </c>
+      <c r="C65" s="25" t="inlineStr">
+        <is>
+          <t>番号なしツール-60</t>
+        </is>
+      </c>
+      <c r="D65" s="25" t="inlineStr">
+        <is>
+          <t>①：補完A-60</t>
+        </is>
+      </c>
+      <c r="E65" s="25" t="inlineStr">
+        <is>
+          <t>③：補完C</t>
+        </is>
+      </c>
+      <c r="F65" s="25" t="inlineStr">
+        <is>
+          <t>共通テキスト</t>
+        </is>
+      </c>
+      <c r="G65" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="H65" s="25" t="n"/>
+    </row>
+    <row r="66" ht="20.4" customHeight="1" s="29">
+      <c r="A66" s="19" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="B66" s="36" t="n">
+        <v>46364</v>
+      </c>
+      <c r="C66" s="25" t="inlineStr">
+        <is>
+          <t>番号なしツール-61</t>
+        </is>
+      </c>
+      <c r="D66" s="25" t="inlineStr">
+        <is>
+          <t>①：補完A-61</t>
+        </is>
+      </c>
+      <c r="E66" s="25" t="inlineStr">
+        <is>
+          <t>③：補完C</t>
+        </is>
+      </c>
+      <c r="F66" s="25" t="inlineStr">
+        <is>
+          <t>共通テキスト</t>
+        </is>
+      </c>
+      <c r="G66" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="H66" s="25" t="n"/>
+    </row>
+    <row r="67" ht="20.4" customHeight="1" s="29">
+      <c r="A67" s="19" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="B67" s="36" t="n">
+        <v>46365</v>
+      </c>
+      <c r="C67" s="25" t="inlineStr">
+        <is>
+          <t>番号なしツール-62</t>
+        </is>
+      </c>
+      <c r="D67" s="25" t="inlineStr">
+        <is>
+          <t>①：補完A-62</t>
+        </is>
+      </c>
+      <c r="E67" s="25" t="inlineStr">
+        <is>
+          <t>③：補完C</t>
+        </is>
+      </c>
+      <c r="F67" s="25" t="inlineStr">
+        <is>
+          <t>共通テキスト</t>
+        </is>
+      </c>
+      <c r="G67" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="H67" s="25" t="n"/>
+    </row>
+    <row r="68" ht="20.4" customHeight="1" s="29">
+      <c r="A68" s="19" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="B68" s="36" t="n">
+        <v>46366</v>
+      </c>
+      <c r="C68" s="25" t="inlineStr">
+        <is>
+          <t>番号なしツール-63</t>
+        </is>
+      </c>
+      <c r="D68" s="25" t="inlineStr">
+        <is>
+          <t>①：補完A-63</t>
+        </is>
+      </c>
+      <c r="E68" s="25" t="inlineStr">
+        <is>
+          <t>③：補完C</t>
+        </is>
+      </c>
+      <c r="F68" s="25" t="inlineStr">
+        <is>
+          <t>共通テキスト</t>
+        </is>
+      </c>
+      <c r="G68" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="H68" s="25" t="n"/>
+    </row>
+    <row r="69" ht="20.4" customHeight="1" s="29">
+      <c r="A69" s="19" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="B69" s="36" t="n">
+        <v>46367</v>
+      </c>
+      <c r="C69" s="25" t="inlineStr">
+        <is>
+          <t>番号なしツール-64</t>
+        </is>
+      </c>
+      <c r="D69" s="25" t="inlineStr">
+        <is>
+          <t>①：補完A-64</t>
+        </is>
+      </c>
+      <c r="E69" s="25" t="inlineStr">
+        <is>
+          <t>③：補完C</t>
+        </is>
+      </c>
+      <c r="F69" s="25" t="inlineStr">
+        <is>
+          <t>共通テキスト</t>
+        </is>
+      </c>
+      <c r="G69" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="H69" s="25" t="n"/>
+    </row>
+    <row r="70" ht="20.4" customHeight="1" s="29">
+      <c r="A70" s="19" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="B70" s="36" t="n">
+        <v>46368</v>
+      </c>
+      <c r="C70" s="25" t="inlineStr">
+        <is>
+          <t>番号なしツール-65</t>
+        </is>
+      </c>
+      <c r="D70" s="25" t="inlineStr">
+        <is>
+          <t>①：補完A-65</t>
+        </is>
+      </c>
+      <c r="E70" s="25" t="inlineStr">
+        <is>
+          <t>③：補完C</t>
+        </is>
+      </c>
+      <c r="F70" s="25" t="inlineStr">
+        <is>
+          <t>共通テキスト</t>
+        </is>
+      </c>
+      <c r="G70" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="H70" s="25" t="n"/>
+    </row>
+    <row r="71" ht="20.4" customHeight="1" s="29">
+      <c r="A71" s="19" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="B71" s="36" t="n">
+        <v>46369</v>
+      </c>
+      <c r="C71" s="25" t="inlineStr">
+        <is>
+          <t>⑪高位ツール</t>
+        </is>
+      </c>
+      <c r="D71" s="25" t="inlineStr">
+        <is>
+          <t>⑪：番号11のテキスト</t>
+        </is>
+      </c>
+      <c r="E71" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="F71" s="25" t="inlineStr">
+        <is>
+          <t>共通文</t>
+        </is>
+      </c>
+      <c r="G71" s="25" t="n"/>
+      <c r="H71" s="25" t="n"/>
+    </row>
+    <row r="72" ht="20.4" customHeight="1" s="29">
+      <c r="A72" s="19" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="B72" s="36" t="n">
+        <v>46370</v>
+      </c>
+      <c r="C72" s="25" t="inlineStr">
+        <is>
+          <t>⑫高位ツール</t>
+        </is>
+      </c>
+      <c r="D72" s="25" t="inlineStr">
+        <is>
+          <t>⑫：番号12のテキスト</t>
+        </is>
+      </c>
+      <c r="E72" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="F72" s="25" t="inlineStr">
+        <is>
+          <t>共通文</t>
+        </is>
+      </c>
+      <c r="G72" s="25" t="n"/>
+      <c r="H72" s="25" t="n"/>
+    </row>
+    <row r="73" ht="20.4" customHeight="1" s="29">
+      <c r="A73" s="19" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="B73" s="36" t="n">
+        <v>46371</v>
+      </c>
+      <c r="C73" s="25" t="inlineStr">
+        <is>
+          <t>⑬高位ツール</t>
+        </is>
+      </c>
+      <c r="D73" s="25" t="inlineStr">
+        <is>
+          <t>⑬：番号13のテキスト</t>
+        </is>
+      </c>
+      <c r="E73" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="F73" s="25" t="inlineStr">
+        <is>
+          <t>共通文</t>
+        </is>
+      </c>
+      <c r="G73" s="25" t="n"/>
+      <c r="H73" s="25" t="n"/>
+    </row>
+    <row r="74" ht="20.4" customHeight="1" s="29">
+      <c r="A74" s="19" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="B74" s="36" t="n">
+        <v>46372</v>
+      </c>
+      <c r="C74" s="25" t="inlineStr">
+        <is>
+          <t>⑭高位ツール</t>
+        </is>
+      </c>
+      <c r="D74" s="25" t="inlineStr">
+        <is>
+          <t>⑭：番号14のテキスト</t>
+        </is>
+      </c>
+      <c r="E74" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="F74" s="25" t="inlineStr">
+        <is>
+          <t>共通文</t>
+        </is>
+      </c>
+      <c r="G74" s="25" t="n"/>
+      <c r="H74" s="25" t="n"/>
+    </row>
+    <row r="75" ht="20.4" customHeight="1" s="29">
+      <c r="A75" s="19" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="B75" s="36" t="n">
+        <v>46373</v>
+      </c>
+      <c r="C75" s="25" t="inlineStr">
+        <is>
+          <t>⑮高位ツール</t>
+        </is>
+      </c>
+      <c r="D75" s="25" t="inlineStr">
+        <is>
+          <t>⑮：番号15のテキスト</t>
+        </is>
+      </c>
+      <c r="E75" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="F75" s="25" t="inlineStr">
+        <is>
+          <t>共通文</t>
+        </is>
+      </c>
+      <c r="G75" s="25" t="n"/>
+      <c r="H75" s="25" t="n"/>
+    </row>
+    <row r="76" ht="20.4" customHeight="1" s="29">
+      <c r="A76" s="19" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="B76" s="36" t="n">
+        <v>46374</v>
+      </c>
+      <c r="C76" s="25" t="inlineStr">
+        <is>
+          <t>⑯高位ツール</t>
+        </is>
+      </c>
+      <c r="D76" s="25" t="inlineStr">
+        <is>
+          <t>⑯：番号16のテキスト</t>
+        </is>
+      </c>
+      <c r="E76" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="F76" s="25" t="inlineStr">
+        <is>
+          <t>共通文</t>
+        </is>
+      </c>
+      <c r="G76" s="25" t="n"/>
+      <c r="H76" s="25" t="n"/>
+    </row>
+    <row r="77" ht="20.4" customHeight="1" s="29">
+      <c r="A77" s="19" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="B77" s="36" t="n">
+        <v>46375</v>
+      </c>
+      <c r="C77" s="25" t="inlineStr">
+        <is>
+          <t>⑰高位ツール</t>
+        </is>
+      </c>
+      <c r="D77" s="25" t="inlineStr">
+        <is>
+          <t>⑰：番号17のテキスト</t>
+        </is>
+      </c>
+      <c r="E77" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="F77" s="25" t="inlineStr">
+        <is>
+          <t>共通文</t>
+        </is>
+      </c>
+      <c r="G77" s="25" t="n"/>
+      <c r="H77" s="25" t="n"/>
+    </row>
+    <row r="78" ht="20.4" customHeight="1" s="29">
+      <c r="A78" s="19" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="B78" s="36" t="n">
+        <v>46376</v>
+      </c>
+      <c r="C78" s="25" t="inlineStr">
+        <is>
+          <t>⑱高位ツール</t>
+        </is>
+      </c>
+      <c r="D78" s="25" t="inlineStr">
+        <is>
+          <t>⑱：番号18のテキスト</t>
+        </is>
+      </c>
+      <c r="E78" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="F78" s="25" t="inlineStr">
+        <is>
+          <t>共通文</t>
+        </is>
+      </c>
+      <c r="G78" s="25" t="n"/>
+      <c r="H78" s="25" t="n"/>
+    </row>
+    <row r="79" ht="20.4" customHeight="1" s="29">
+      <c r="A79" s="19" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="B79" s="36" t="n">
+        <v>46377</v>
+      </c>
+      <c r="C79" s="25" t="inlineStr">
+        <is>
+          <t>⑲高位ツール</t>
+        </is>
+      </c>
+      <c r="D79" s="25" t="inlineStr">
+        <is>
+          <t>⑲：番号19のテキスト</t>
+        </is>
+      </c>
+      <c r="E79" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="F79" s="25" t="inlineStr">
+        <is>
+          <t>共通文</t>
+        </is>
+      </c>
+      <c r="G79" s="25" t="n"/>
+      <c r="H79" s="25" t="n"/>
+    </row>
+    <row r="80" ht="20.4" customHeight="1" s="29">
+      <c r="A80" s="19" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="B80" s="36" t="n">
+        <v>46378</v>
+      </c>
+      <c r="C80" s="25" t="inlineStr">
+        <is>
+          <t>⑳高位ツール</t>
+        </is>
+      </c>
+      <c r="D80" s="25" t="inlineStr">
+        <is>
+          <t>⑳：番号20のテキスト</t>
+        </is>
+      </c>
+      <c r="E80" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="F80" s="25" t="inlineStr">
+        <is>
+          <t>共通文</t>
+        </is>
+      </c>
+      <c r="G80" s="25" t="n"/>
+      <c r="H80" s="25" t="n"/>
+    </row>
+    <row r="81" ht="20.4" customHeight="1" s="29">
+      <c r="A81" s="19" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="B81" s="36" t="n">
+        <v>46379</v>
+      </c>
+      <c r="C81" s="25" t="inlineStr">
+        <is>
+          <t>㉑高位ツール</t>
+        </is>
+      </c>
+      <c r="D81" s="25" t="inlineStr">
+        <is>
+          <t>㉑：番号21のテキスト</t>
+        </is>
+      </c>
+      <c r="E81" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="F81" s="25" t="inlineStr">
+        <is>
+          <t>共通文</t>
+        </is>
+      </c>
+      <c r="G81" s="25" t="n"/>
+      <c r="H81" s="25" t="n"/>
+    </row>
+    <row r="82" ht="20.4" customHeight="1" s="29">
+      <c r="A82" s="19" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="B82" s="36" t="n">
+        <v>46380</v>
+      </c>
+      <c r="C82" s="25" t="inlineStr">
+        <is>
+          <t>㉒高位ツール</t>
+        </is>
+      </c>
+      <c r="D82" s="25" t="inlineStr">
+        <is>
+          <t>㉒：番号22のテキスト</t>
+        </is>
+      </c>
+      <c r="E82" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="F82" s="25" t="inlineStr">
+        <is>
+          <t>共通文</t>
+        </is>
+      </c>
+      <c r="G82" s="25" t="n"/>
+      <c r="H82" s="25" t="n"/>
+    </row>
+    <row r="83" ht="20.4" customHeight="1" s="29">
+      <c r="A83" s="19" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="B83" s="36" t="n">
+        <v>46381</v>
+      </c>
+      <c r="C83" s="25" t="inlineStr">
+        <is>
+          <t>㉓高位ツール</t>
+        </is>
+      </c>
+      <c r="D83" s="25" t="inlineStr">
+        <is>
+          <t>㉓：番号23のテキスト</t>
+        </is>
+      </c>
+      <c r="E83" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="F83" s="25" t="inlineStr">
+        <is>
+          <t>共通文</t>
+        </is>
+      </c>
+      <c r="G83" s="25" t="n"/>
+      <c r="H83" s="25" t="n"/>
+    </row>
+    <row r="84" ht="20.4" customHeight="1" s="29">
+      <c r="A84" s="19" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="B84" s="36" t="n">
+        <v>46382</v>
+      </c>
+      <c r="C84" s="25" t="inlineStr">
+        <is>
+          <t>㉔高位ツール</t>
+        </is>
+      </c>
+      <c r="D84" s="25" t="inlineStr">
+        <is>
+          <t>㉔：番号24のテキスト</t>
+        </is>
+      </c>
+      <c r="E84" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="F84" s="25" t="inlineStr">
+        <is>
+          <t>共通文</t>
+        </is>
+      </c>
+      <c r="G84" s="25" t="n"/>
+      <c r="H84" s="25" t="n"/>
+    </row>
+    <row r="85" ht="20.4" customHeight="1" s="29">
+      <c r="A85" s="19" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="B85" s="36" t="n">
+        <v>46383</v>
+      </c>
+      <c r="C85" s="25" t="inlineStr">
+        <is>
+          <t>㉕高位ツール</t>
+        </is>
+      </c>
+      <c r="D85" s="25" t="inlineStr">
+        <is>
+          <t>㉕：番号25のテキスト</t>
+        </is>
+      </c>
+      <c r="E85" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="F85" s="25" t="inlineStr">
+        <is>
+          <t>共通文</t>
+        </is>
+      </c>
+      <c r="G85" s="25" t="n"/>
+      <c r="H85" s="25" t="n"/>
+    </row>
+    <row r="86" ht="20.4" customHeight="1" s="29">
+      <c r="A86" s="19" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="B86" s="36" t="n">
+        <v>46384</v>
+      </c>
+      <c r="C86" s="25" t="inlineStr">
+        <is>
+          <t>㉖高位ツール</t>
+        </is>
+      </c>
+      <c r="D86" s="25" t="inlineStr">
+        <is>
+          <t>㉖：番号26のテキスト</t>
+        </is>
+      </c>
+      <c r="E86" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="F86" s="25" t="inlineStr">
+        <is>
+          <t>共通文</t>
+        </is>
+      </c>
+      <c r="G86" s="25" t="n"/>
+      <c r="H86" s="25" t="n"/>
+    </row>
+    <row r="87" ht="20.4" customHeight="1" s="29">
+      <c r="A87" s="19" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="B87" s="36" t="n">
+        <v>46385</v>
+      </c>
+      <c r="C87" s="25" t="inlineStr">
+        <is>
+          <t>㉗高位ツール</t>
+        </is>
+      </c>
+      <c r="D87" s="25" t="inlineStr">
+        <is>
+          <t>㉗：番号27のテキスト</t>
+        </is>
+      </c>
+      <c r="E87" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="F87" s="25" t="inlineStr">
+        <is>
+          <t>共通文</t>
+        </is>
+      </c>
+      <c r="G87" s="25" t="n"/>
+      <c r="H87" s="25" t="n"/>
+    </row>
+    <row r="88" ht="20.4" customHeight="1" s="29">
+      <c r="A88" s="19" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="B88" s="36" t="n">
+        <v>46386</v>
+      </c>
+      <c r="C88" s="25" t="inlineStr">
+        <is>
+          <t>㉘高位ツール</t>
+        </is>
+      </c>
+      <c r="D88" s="25" t="inlineStr">
+        <is>
+          <t>㉘：番号28のテキスト</t>
+        </is>
+      </c>
+      <c r="E88" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="F88" s="25" t="inlineStr">
+        <is>
+          <t>共通文</t>
+        </is>
+      </c>
+      <c r="G88" s="25" t="n"/>
+      <c r="H88" s="25" t="n"/>
+    </row>
+    <row r="89" ht="20.4" customHeight="1" s="29">
+      <c r="A89" s="19" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="B89" s="36" t="n">
+        <v>46387</v>
+      </c>
+      <c r="C89" s="25" t="inlineStr">
+        <is>
+          <t>㉙高位ツール</t>
+        </is>
+      </c>
+      <c r="D89" s="25" t="inlineStr">
+        <is>
+          <t>㉙：番号29のテキスト</t>
+        </is>
+      </c>
+      <c r="E89" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="F89" s="25" t="inlineStr">
+        <is>
+          <t>共通文</t>
+        </is>
+      </c>
+      <c r="G89" s="25" t="n"/>
+      <c r="H89" s="25" t="n"/>
+    </row>
+    <row r="90" ht="20.4" customHeight="1" s="29">
+      <c r="A90" s="19" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="B90" s="36" t="n">
+        <v>46388</v>
+      </c>
+      <c r="C90" s="25" t="inlineStr">
+        <is>
+          <t>㉚高位ツール</t>
+        </is>
+      </c>
+      <c r="D90" s="25" t="inlineStr">
+        <is>
+          <t>㉚：番号30のテキスト</t>
+        </is>
+      </c>
+      <c r="E90" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="F90" s="25" t="inlineStr">
+        <is>
+          <t>共通文</t>
+        </is>
+      </c>
+      <c r="G90" s="25" t="n"/>
+      <c r="H90" s="25" t="n"/>
+    </row>
+    <row r="91" ht="20.4" customHeight="1" s="29">
+      <c r="A91" s="19" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="B91" s="36" t="n">
+        <v>46389</v>
+      </c>
+      <c r="C91" s="25" t="inlineStr">
+        <is>
+          <t>1ツールA</t>
+        </is>
+      </c>
+      <c r="D91" s="25" t="inlineStr">
+        <is>
+          <t>通常テキスト</t>
+        </is>
+      </c>
+      <c r="E91" s="25" t="inlineStr">
+        <is>
+          <t>通常テキスト</t>
+        </is>
+      </c>
+      <c r="F91" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="G91" s="25" t="inlineStr">
+        <is>
+          <t>通常テキスト</t>
+        </is>
+      </c>
+      <c r="H91" s="25" t="n"/>
+    </row>
+    <row r="92" ht="20.4" customHeight="1" s="29">
+      <c r="A92" s="19" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="B92" s="36" t="n">
+        <v>46390</v>
+      </c>
+      <c r="C92" s="25" t="inlineStr">
+        <is>
+          <t>⑳〜①ツールB</t>
+        </is>
+      </c>
+      <c r="D92" s="25" t="inlineStr">
+        <is>
+          <t>逆順範囲</t>
+        </is>
+      </c>
+      <c r="E92" s="25" t="inlineStr">
+        <is>
+          <t>通常テキスト</t>
+        </is>
+      </c>
+      <c r="F92" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="G92" s="25" t="inlineStr">
+        <is>
+          <t>通常テキスト</t>
+        </is>
+      </c>
+      <c r="H92" s="25" t="n"/>
+    </row>
+    <row r="93" ht="20.4" customHeight="1" s="29">
+      <c r="A93" s="19" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="B93" s="36" t="n">
+        <v>46391</v>
+      </c>
+      <c r="C93" s="25" t="inlineStr">
+        <is>
+          <t>⑫:</t>
+        </is>
+      </c>
+      <c r="D93" s="25" t="inlineStr">
+        <is>
+          <t>番号だけで本文なし</t>
+        </is>
+      </c>
+      <c r="E93" s="25" t="inlineStr">
+        <is>
+          <t>通常テキスト</t>
+        </is>
+      </c>
+      <c r="F93" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="G93" s="25" t="inlineStr">
+        <is>
+          <t>通常テキスト</t>
+        </is>
+      </c>
+      <c r="H93" s="25" t="n"/>
+    </row>
+    <row r="94" ht="20.4" customHeight="1" s="29">
+      <c r="A94" s="19" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="B94" s="36" t="n">
+        <v>46392</v>
+      </c>
+      <c r="C94" s="25" t="inlineStr">
+        <is>
+          <t>通常ツール㉛</t>
+        </is>
+      </c>
+      <c r="D94" s="25" t="inlineStr">
+        <is>
+          <t>㉛：未登録番号</t>
+        </is>
+      </c>
+      <c r="E94" s="25" t="inlineStr">
+        <is>
+          <t>通常テキスト</t>
+        </is>
+      </c>
+      <c r="F94" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="G94" s="25" t="inlineStr">
+        <is>
+          <t>通常テキスト</t>
+        </is>
+      </c>
+      <c r="H94" s="25" t="n"/>
+    </row>
+    <row r="95" ht="20.4" customHeight="1" s="29">
+      <c r="A95" s="19" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B95" s="36" t="n">
+        <v>46393</v>
+      </c>
+      <c r="C95" s="25" t="n"/>
+      <c r="D95" s="25" t="inlineStr">
+        <is>
+          <t>⑧：ツール欄が空の補完</t>
+        </is>
+      </c>
+      <c r="E95" s="25" t="inlineStr">
+        <is>
+          <t>通常テキスト</t>
+        </is>
+      </c>
+      <c r="F95" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="G95" s="25" t="inlineStr">
+        <is>
+          <t>通常テキスト</t>
+        </is>
+      </c>
+      <c r="H95" s="25" t="n"/>
+    </row>
+    <row r="96" ht="20.4" customHeight="1" s="29">
+      <c r="A96" s="19" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="B96" s="36" t="n">
+        <v>46394</v>
+      </c>
+      <c r="C96" s="25" t="inlineStr">
+        <is>
+          <t>番号なしツール-91</t>
+        </is>
+      </c>
+      <c r="D96" s="25" t="inlineStr">
+        <is>
+          <t>通常テキスト-91</t>
+        </is>
+      </c>
+      <c r="E96" s="25" t="inlineStr">
+        <is>
+          <t>共通メモ-91</t>
+        </is>
+      </c>
+      <c r="F96" s="25" t="inlineStr">
+        <is>
+          <t>補足</t>
+        </is>
+      </c>
+      <c r="G96" s="25" t="inlineStr">
+        <is>
+          <t>通常文</t>
+        </is>
+      </c>
+      <c r="H96" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="20.4" customHeight="1" s="29">
+      <c r="A97" s="19" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="B97" s="36" t="n">
+        <v>46395</v>
+      </c>
+      <c r="C97" s="25" t="inlineStr">
+        <is>
+          <t>番号なしツール-92</t>
+        </is>
+      </c>
+      <c r="D97" s="25" t="inlineStr">
+        <is>
+          <t>通常テキスト-92</t>
+        </is>
+      </c>
+      <c r="E97" s="25" t="inlineStr">
+        <is>
+          <t>共通メモ-92</t>
+        </is>
+      </c>
+      <c r="F97" s="25" t="inlineStr">
+        <is>
+          <t>補足</t>
+        </is>
+      </c>
+      <c r="G97" s="25" t="inlineStr">
+        <is>
+          <t>通常文</t>
+        </is>
+      </c>
+      <c r="H97" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="20.4" customHeight="1" s="29">
+      <c r="A98" s="19" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="B98" s="36" t="n">
+        <v>46396</v>
+      </c>
+      <c r="C98" s="25" t="inlineStr">
+        <is>
+          <t>番号なしツール-93</t>
+        </is>
+      </c>
+      <c r="D98" s="25" t="inlineStr">
+        <is>
+          <t>通常テキスト-93</t>
+        </is>
+      </c>
+      <c r="E98" s="25" t="inlineStr">
+        <is>
+          <t>共通メモ-93</t>
+        </is>
+      </c>
+      <c r="F98" s="25" t="inlineStr">
+        <is>
+          <t>補足</t>
+        </is>
+      </c>
+      <c r="G98" s="25" t="inlineStr">
+        <is>
+          <t>通常文</t>
+        </is>
+      </c>
+      <c r="H98" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="20.4" customHeight="1" s="29">
+      <c r="A99" s="19" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="B99" s="36" t="n">
+        <v>46397</v>
+      </c>
+      <c r="C99" s="25" t="inlineStr">
+        <is>
+          <t>番号なしツール-94</t>
+        </is>
+      </c>
+      <c r="D99" s="25" t="inlineStr">
+        <is>
+          <t>通常テキスト-94</t>
+        </is>
+      </c>
+      <c r="E99" s="25" t="inlineStr">
+        <is>
+          <t>共通メモ-94</t>
+        </is>
+      </c>
+      <c r="F99" s="25" t="inlineStr">
+        <is>
+          <t>補足</t>
+        </is>
+      </c>
+      <c r="G99" s="25" t="inlineStr">
+        <is>
+          <t>通常文</t>
+        </is>
+      </c>
+      <c r="H99" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="20.4" customHeight="1" s="29">
+      <c r="A100" s="19" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="B100" s="36" t="n">
+        <v>46398</v>
+      </c>
+      <c r="C100" s="25" t="inlineStr">
+        <is>
+          <t>番号なしツール-95</t>
+        </is>
+      </c>
+      <c r="D100" s="25" t="inlineStr">
+        <is>
+          <t>通常テキスト-95</t>
+        </is>
+      </c>
+      <c r="E100" s="25" t="inlineStr">
+        <is>
+          <t>共通メモ-95</t>
+        </is>
+      </c>
+      <c r="F100" s="25" t="inlineStr">
+        <is>
+          <t>補足</t>
+        </is>
+      </c>
+      <c r="G100" s="25" t="inlineStr">
+        <is>
+          <t>通常文</t>
+        </is>
+      </c>
+      <c r="H100" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="20.4" customHeight="1" s="29">
+      <c r="A101" s="19" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="B101" s="36" t="n">
+        <v>46399</v>
+      </c>
+      <c r="C101" s="25" t="inlineStr">
+        <is>
+          <t>番号なしツール-96</t>
+        </is>
+      </c>
+      <c r="D101" s="25" t="inlineStr">
+        <is>
+          <t>通常テキスト-96</t>
+        </is>
+      </c>
+      <c r="E101" s="25" t="inlineStr">
+        <is>
+          <t>共通メモ-96</t>
+        </is>
+      </c>
+      <c r="F101" s="25" t="inlineStr">
+        <is>
+          <t>補足</t>
+        </is>
+      </c>
+      <c r="G101" s="25" t="inlineStr">
+        <is>
+          <t>通常文</t>
+        </is>
+      </c>
+      <c r="H101" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="20.4" customHeight="1" s="29">
+      <c r="A102" s="19" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="B102" s="36" t="n">
+        <v>46400</v>
+      </c>
+      <c r="C102" s="25" t="inlineStr">
+        <is>
+          <t>番号なしツール-97</t>
+        </is>
+      </c>
+      <c r="D102" s="25" t="inlineStr">
+        <is>
+          <t>通常テキスト-97</t>
+        </is>
+      </c>
+      <c r="E102" s="25" t="inlineStr">
+        <is>
+          <t>共通メモ-97</t>
+        </is>
+      </c>
+      <c r="F102" s="25" t="inlineStr">
+        <is>
+          <t>補足</t>
+        </is>
+      </c>
+      <c r="G102" s="25" t="inlineStr">
+        <is>
+          <t>通常文</t>
+        </is>
+      </c>
+      <c r="H102" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="20.4" customHeight="1" s="29">
+      <c r="A103" s="19" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="B103" s="36" t="n">
+        <v>46401</v>
+      </c>
+      <c r="C103" s="25" t="inlineStr">
+        <is>
+          <t>番号なしツール-98</t>
+        </is>
+      </c>
+      <c r="D103" s="25" t="inlineStr">
+        <is>
+          <t>通常テキスト-98</t>
+        </is>
+      </c>
+      <c r="E103" s="25" t="inlineStr">
+        <is>
+          <t>共通メモ-98</t>
+        </is>
+      </c>
+      <c r="F103" s="25" t="inlineStr">
+        <is>
+          <t>補足</t>
+        </is>
+      </c>
+      <c r="G103" s="25" t="inlineStr">
+        <is>
+          <t>通常文</t>
+        </is>
+      </c>
+      <c r="H103" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="20.4" customHeight="1" s="29">
+      <c r="A104" s="19" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="B104" s="36" t="n">
+        <v>46402</v>
+      </c>
+      <c r="C104" s="25" t="inlineStr">
+        <is>
+          <t>番号なしツール-99</t>
+        </is>
+      </c>
+      <c r="D104" s="25" t="inlineStr">
+        <is>
+          <t>通常テキスト-99</t>
+        </is>
+      </c>
+      <c r="E104" s="25" t="inlineStr">
+        <is>
+          <t>共通メモ-99</t>
+        </is>
+      </c>
+      <c r="F104" s="25" t="inlineStr">
+        <is>
+          <t>補足</t>
+        </is>
+      </c>
+      <c r="G104" s="25" t="inlineStr">
+        <is>
+          <t>通常文</t>
+        </is>
+      </c>
+      <c r="H104" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="20.4" customHeight="1" s="29">
+      <c r="A105" s="19" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="B105" s="36" t="n">
+        <v>46403</v>
+      </c>
+      <c r="C105" s="25" t="inlineStr">
+        <is>
+          <t>番号なしツール-100</t>
+        </is>
+      </c>
+      <c r="D105" s="25" t="inlineStr">
+        <is>
+          <t>通常テキスト-100</t>
+        </is>
+      </c>
+      <c r="E105" s="25" t="inlineStr">
+        <is>
+          <t>共通メモ-100</t>
+        </is>
+      </c>
+      <c r="F105" s="25" t="inlineStr">
+        <is>
+          <t>補足</t>
+        </is>
+      </c>
+      <c r="G105" s="25" t="inlineStr">
+        <is>
+          <t>通常文</t>
+        </is>
+      </c>
+      <c r="H105" s="25" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:H2"/>
   </mergeCells>
   <pageMargins left="0.458333" right="0.458333" top="0.25" bottom="1" header="0.25" footer="0.25"/>
-  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="landscape" pageOrder="downThenOver"/>
+  <pageSetup orientation="landscape" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="0" pageOrder="downThenOver"/>
   <headerFooter>
-    <oddFooter>&amp;C&amp;"ヒラギノ角ゴ ProN W3,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;"ヒラギノ角ゴ ProN W3,Regular"&amp;12 &amp;K000000&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
   </headerFooter>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>